--- a/templates/BNY11756 - template.xlsx
+++ b/templates/BNY11756 - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$H$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$H$44</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1314,14 +1314,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.28515625" defaultRowHeight="12.75"/>
   <cols>
     <col width="17.28515625" customWidth="1" style="60" min="1" max="1"/>
     <col width="18.7109375" customWidth="1" style="60" min="2" max="8"/>
     <col width="21.5703125" customWidth="1" style="60" min="9" max="9"/>
-    <col width="17.28515625" customWidth="1" style="60" min="10" max="19"/>
-    <col width="17.28515625" customWidth="1" style="60" min="20" max="16384"/>
+    <col width="17.28515625" customWidth="1" style="60" min="10" max="20"/>
+    <col width="17.28515625" customWidth="1" style="60" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1505,52 +1505,52 @@
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="10">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>1.42140989</v>
+        <v>1.43756662</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>-0.001434674218186438</v>
+        <v>0.0005455034489032506</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>-0.002775113762013337</v>
+        <v>0.003784363932781476</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>0.001340439543826899</v>
+        <v>-0.003238860483878225</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>-0.0004173049558622299</v>
+        <v>0.001228260330804476</v>
       </c>
       <c r="H18" s="29" t="n">
-        <v>-0.001017369262324208</v>
+        <v>-0.0006827568819012253</v>
       </c>
     </row>
     <row r="19" ht="15.95" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C19" s="31" t="n">
-        <v>1.42345208</v>
+        <v>1.43678285</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>0.00170094335045845</v>
+        <v>9.679504478965484e-05</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>0.001280962415003195</v>
+        <v>0.001906502045387226</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>0.0004199809354552553</v>
+        <v>-0.001809707000597571</v>
       </c>
       <c r="G19" s="32" t="n">
-        <v>0.001008317718015572</v>
+        <v>0.001228864396657148</v>
       </c>
       <c r="H19" s="32" t="n">
-        <v>0.0006926256324428781</v>
+        <v>-0.001132069351867493</v>
       </c>
       <c r="I19" s="4" t="n"/>
     </row>
@@ -1558,26 +1558,26 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C20" s="31" t="n">
-        <v>1.42103498</v>
+        <v>1.43664379</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>-0.00140132060546061</v>
+        <v>0.004275696131599283</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>-0.002016246470113892</v>
+        <v>0.005962594715911873</v>
       </c>
       <c r="F20" s="32" t="n">
-        <v>0.0006149258646532818</v>
+        <v>-0.001686898584312591</v>
       </c>
       <c r="G20" s="32" t="n">
-        <v>-0.000369098634551146</v>
+        <v>0.003055672154189226</v>
       </c>
       <c r="H20" s="32" t="n">
-        <v>-0.001032221970909464</v>
+        <v>0.001220023977410056</v>
       </c>
       <c r="I20" s="4" t="n"/>
     </row>
@@ -1585,26 +1585,26 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>1.4230291</v>
+        <v>1.43052729</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>0.002110607411183851</v>
+        <v>-0.0008781139531216509</v>
       </c>
       <c r="E21" s="32" t="n">
-        <v>0.002323937513367902</v>
+        <v>-8.847376162690601e-05</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>-0.0002133301021840506</v>
+        <v>-0.0007896401914947448</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>0.002424076115274953</v>
+        <v>0.0001401648621799367</v>
       </c>
       <c r="H21" s="32" t="n">
-        <v>-0.0003134687040911022</v>
+        <v>-0.001018278815301588</v>
       </c>
       <c r="I21" s="4" t="n"/>
     </row>
@@ -1612,26 +1612,26 @@
       <c r="A22" s="11" t="n"/>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C22" s="31" t="n">
-        <v>1.42003197</v>
+        <v>1.43178456</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>-0.001954066686972067</v>
+        <v>0.001517639449370112</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>-0.003517165775007047</v>
+        <v>0.001373673909628392</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>0.00156309908803498</v>
+        <v>0.0001439655397417194</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>-0.001141971242602069</v>
+        <v>-7.902904525247667e-05</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>-0.0008120954443699979</v>
+        <v>0.001596668494622588</v>
       </c>
       <c r="I22" s="4" t="n"/>
     </row>
@@ -1685,24 +1685,24 @@
       <c r="A25" s="11" t="n"/>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C25" s="43" t="inlineStr"/>
       <c r="D25" s="43" t="n">
-        <v>-0.006526024608487946</v>
+        <v>0.006298577162552554</v>
       </c>
       <c r="E25" s="29" t="n">
-        <v>-0.008025264155480549</v>
+        <v>0.0157814657880031</v>
       </c>
       <c r="F25" s="29" t="n">
-        <v>0.001499239546992603</v>
+        <v>-0.009482888625450547</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>0.006369420073854881</v>
+        <v>0.007488477748118338</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>-0.01289544468234283</v>
+        <v>-0.001189900585565784</v>
       </c>
       <c r="I25" s="15" t="n"/>
     </row>
@@ -1715,19 +1715,19 @@
       </c>
       <c r="C26" s="44" t="inlineStr"/>
       <c r="D26" s="44" t="n">
-        <v>-0.004636307953831853</v>
+        <v>0.009288343293558876</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>-0.004366530544361868</v>
+        <v>0.02260048556561456</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>-0.0002697774094699845</v>
+        <v>-0.01331214227205568</v>
       </c>
       <c r="G26" s="32" t="n">
-        <v>0.008564754015659926</v>
+        <v>0.02051942488737701</v>
       </c>
       <c r="H26" s="32" t="n">
-        <v>-0.01320106196949178</v>
+        <v>-0.01123108159381814</v>
       </c>
       <c r="I26" s="41" t="n"/>
     </row>
@@ -1740,19 +1740,19 @@
       </c>
       <c r="C27" s="44" t="inlineStr"/>
       <c r="D27" s="44" t="n">
-        <v>0.02639746808699805</v>
+        <v>0.03248444875760725</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>0.02705013376004373</v>
+        <v>0.04800146190063681</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>-0.0006526656730456715</v>
+        <v>-0.01551701314302956</v>
       </c>
       <c r="G27" s="32" t="n">
-        <v>0.03540704738942546</v>
+        <v>0.04413395526982056</v>
       </c>
       <c r="H27" s="32" t="n">
-        <v>-0.009009579302427406</v>
+        <v>-0.0116495065122133</v>
       </c>
       <c r="I27" s="16" t="n"/>
     </row>
@@ -1765,19 +1765,19 @@
       </c>
       <c r="C28" s="44" t="inlineStr"/>
       <c r="D28" s="44" t="n">
-        <v>0.0531474099748237</v>
+        <v>0.062972536406527</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>0.05228677744302912</v>
+        <v>0.08424100868653972</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>0.0008606325317945807</v>
+        <v>-0.02126847228001272</v>
       </c>
       <c r="G28" s="32" t="n">
-        <v>0.06212331211768896</v>
+        <v>0.07820231730317562</v>
       </c>
       <c r="H28" s="32" t="n">
-        <v>-0.008975902142865255</v>
+        <v>-0.01522978089664861</v>
       </c>
       <c r="I28" s="16" t="n"/>
     </row>
@@ -1790,19 +1790,19 @@
       </c>
       <c r="C29" s="44" t="inlineStr"/>
       <c r="D29" s="44" t="n">
-        <v>0.1206754284468305</v>
+        <v>0.1270485490492748</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>0.1198792525684791</v>
+        <v>0.1412381166231067</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>0.0007961758783514572</v>
+        <v>-0.01418956757383194</v>
       </c>
       <c r="G29" s="32" t="n">
-        <v>0.1176647437940919</v>
+        <v>0.1297857302122285</v>
       </c>
       <c r="H29" s="32" t="n">
-        <v>0.003010684652738682</v>
+        <v>-0.002737181162953739</v>
       </c>
       <c r="I29" s="16" t="n"/>
     </row>
@@ -1810,24 +1810,24 @@
       <c r="A30" s="11" t="n"/>
       <c r="B30" s="49" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C30" s="44" t="inlineStr"/>
       <c r="D30" s="44" t="n">
-        <v>0.02096353089627923</v>
+        <v>0.1861899659844537</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>0.01985296752187793</v>
+        <v>0.1602720665516928</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>0.001110563374401297</v>
+        <v>0.0259178994327609</v>
       </c>
       <c r="G30" s="32" t="n">
-        <v>0.03089355229913116</v>
+        <v>0.2160979564480416</v>
       </c>
       <c r="H30" s="32" t="n">
-        <v>-0.00993002140285193</v>
+        <v>-0.02990799046358794</v>
       </c>
       <c r="I30" s="16" t="n"/>
     </row>
@@ -1835,130 +1835,138 @@
       <c r="A31" s="11" t="n"/>
       <c r="B31" s="49" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr"/>
       <c r="D31" s="44" t="n">
-        <v>0.1304479302128252</v>
+        <v>0.03256851002621741</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>0.1316812131695793</v>
+        <v>0.04606202995521769</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>-0.001233282956754067</v>
+        <v>-0.01349351992900027</v>
       </c>
       <c r="G31" s="32" t="n">
-        <v>0.1165027532037295</v>
+        <v>0.04642807189443898</v>
       </c>
       <c r="H31" s="32" t="n">
-        <v>0.0139451770090957</v>
+        <v>-0.01385956186822157</v>
       </c>
       <c r="I31" s="16" t="n"/>
     </row>
-    <row r="32" ht="15.95" customFormat="1" customHeight="1" s="31">
-      <c r="A32" s="53" t="n"/>
+    <row r="32" ht="15.95" customHeight="1">
+      <c r="A32" s="11" t="n"/>
       <c r="B32" s="49" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C32" s="44" t="inlineStr"/>
       <c r="D32" s="44" t="n">
-        <v>0.04653108195462896</v>
+        <v>0.1304479302128252</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>-0.02439397265320542</v>
+        <v>0.1316812131695793</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>0.07092505460783438</v>
+        <v>-0.001233282956754067</v>
       </c>
       <c r="G32" s="32" t="n">
-        <v>0.06161563642436141</v>
+        <v>0.1165027532037295</v>
       </c>
       <c r="H32" s="32" t="n">
-        <v>-0.01508455446973245</v>
-      </c>
-    </row>
-    <row r="33" ht="15.95" customHeight="1">
+        <v>0.0139451770090957</v>
+      </c>
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="31">
       <c r="A33" s="53" t="n"/>
       <c r="B33" s="49" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C33" s="44" t="inlineStr"/>
       <c r="D33" s="44" t="n">
-        <v>0.4214098900000001</v>
+        <v>0.04653108195462896</v>
       </c>
       <c r="E33" s="32" t="n">
-        <v>0.3539451011189247</v>
+        <v>-0.02439397265320542</v>
       </c>
       <c r="F33" s="32" t="n">
-        <v>0.06746478888107532</v>
+        <v>0.07092505460783438</v>
       </c>
       <c r="G33" s="32" t="n">
-        <v>0.4215499629686645</v>
+        <v>0.06161563642436141</v>
       </c>
       <c r="H33" s="32" t="n">
-        <v>-0.0001400729686644731</v>
-      </c>
-      <c r="I33" s="16" t="n"/>
+        <v>-0.01508455446973245</v>
+      </c>
     </row>
     <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="17" t="n"/>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="26.1" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="45" t="inlineStr">
+      <c r="A34" s="53" t="n"/>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr"/>
+      <c r="D34" s="44" t="n">
+        <v>0.4375666199999999</v>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>0.3887399517656471</v>
+      </c>
+      <c r="F34" s="32" t="n">
+        <v>0.04882666823435278</v>
+      </c>
+      <c r="G34" s="32" t="n">
+        <v>0.4429712782016442</v>
+      </c>
+      <c r="H34" s="32" t="n">
+        <v>-0.005404658201644263</v>
+      </c>
+      <c r="I34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="15.95" customHeight="1">
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="26.1" customHeight="1">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="45" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C35" s="45" t="n"/>
-      <c r="D35" s="45" t="n"/>
-      <c r="E35" s="45" t="n"/>
-      <c r="F35" s="45" t="n"/>
-      <c r="G35" s="45" t="n"/>
-      <c r="H35" s="45" t="n"/>
-      <c r="I35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="46" t="n">
-        <v>24441385.23</v>
-      </c>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
-      <c r="H36" s="46" t="n"/>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="H36" s="45" t="n"/>
       <c r="I36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="11" t="n"/>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C37" s="34" t="n"/>
       <c r="D37" s="34" t="n"/>
       <c r="E37" s="46" t="n">
-        <v>20654369.68198413</v>
+        <v>24850724.42</v>
       </c>
       <c r="F37" s="46" t="n"/>
       <c r="G37" s="46" t="n"/>
@@ -1967,98 +1975,104 @@
     </row>
     <row r="38" ht="15.95" customHeight="1">
       <c r="A38" s="11" t="n"/>
-      <c r="B38" s="33" t="n"/>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
       <c r="C38" s="34" t="n"/>
       <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="34" t="n"/>
+      <c r="E38" s="46" t="n">
+        <v>20847471.75452381</v>
+      </c>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n"/>
       <c r="I38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="11" t="n"/>
-      <c r="B39" s="36" t="inlineStr">
-        <is>
-          <t>¹ Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C39" s="37" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="38" t="n"/>
-      <c r="H39" s="38" t="n"/>
+      <c r="B39" s="33" t="n"/>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="34" t="n"/>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="34" t="n"/>
+      <c r="G39" s="34" t="n"/>
+      <c r="H39" s="34" t="n"/>
       <c r="I39" s="4" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="11" t="n"/>
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">²Cota Inicial em: </t>
-        </is>
-      </c>
-      <c r="C40" s="39" t="inlineStr">
-        <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="D40" s="40" t="n"/>
-      <c r="E40" s="40" t="n"/>
-      <c r="F40" s="40" t="n"/>
-      <c r="G40" s="40" t="n"/>
-      <c r="H40" s="40" t="n"/>
+      <c r="B40" s="36" t="inlineStr">
+        <is>
+          <t>¹ Data de Referência:</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="38" t="n"/>
+      <c r="H40" s="38" t="n"/>
       <c r="I40" s="4" t="n"/>
     </row>
     <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="11" t="n"/>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="20" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">²Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C41" s="39" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="D41" s="40" t="n"/>
+      <c r="E41" s="40" t="n"/>
+      <c r="F41" s="40" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="40" t="n"/>
       <c r="I41" s="4" t="n"/>
     </row>
-    <row r="42" ht="47.25" customHeight="1">
+    <row r="42" ht="15.95" customHeight="1">
       <c r="A42" s="11" t="n"/>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="21" t="n"/>
+      <c r="I42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="47.25" customHeight="1">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="I42" s="4" t="n"/>
-    </row>
-    <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="59" t="n"/>
       <c r="I43" s="4" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="n"/>
+      <c r="B44" s="59" t="n"/>
       <c r="I44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
-      <c r="B45" s="23" t="n"/>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="16" t="n"/>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
       <c r="I45" s="4" t="n"/>
     </row>
     <row r="46">
@@ -2072,13 +2086,24 @@
       <c r="H46" s="16" t="n"/>
       <c r="I46" s="4" t="n"/>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="16" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47" s="4" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B42:H42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="84"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>